--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="138">
   <si>
     <t>Materia</t>
   </si>
@@ -181,24 +181,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN AL DERECHO</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS SOCIALES</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -936,16 +918,16 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -990,16 +972,16 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1013,16 +995,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -1067,16 +1049,16 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1090,16 +1072,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -1144,16 +1126,16 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1167,16 +1149,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -1221,16 +1203,16 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1244,16 +1226,16 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1298,16 +1280,16 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1321,16 +1303,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -1375,16 +1357,16 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1398,16 +1380,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1452,16 +1434,16 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1475,16 +1457,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1529,16 +1511,16 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1552,16 +1534,16 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1606,16 +1588,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1629,16 +1611,16 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1683,16 +1665,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1706,16 +1688,16 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -1760,16 +1742,16 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1783,16 +1765,16 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>7</v>
@@ -1837,16 +1819,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1860,16 +1842,16 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>9</v>
@@ -1914,16 +1896,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1937,16 +1919,16 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1991,16 +1973,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2014,16 +1996,16 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>9</v>
@@ -2068,16 +2050,16 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2091,16 +2073,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2145,16 +2127,16 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2168,16 +2150,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>7</v>
@@ -2222,16 +2204,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2245,16 +2227,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2299,16 +2281,16 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2322,16 +2304,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -2376,16 +2358,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2399,16 +2381,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -2453,16 +2435,16 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2476,16 +2458,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -2530,16 +2512,16 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2553,16 +2535,16 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>7</v>
@@ -2607,16 +2589,16 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2630,16 +2612,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>9</v>
@@ -2684,16 +2666,16 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2707,16 +2689,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -2761,16 +2743,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2784,16 +2766,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F28">
         <v>9</v>
@@ -2838,16 +2820,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2861,16 +2843,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -2915,16 +2897,16 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2938,16 +2920,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -2992,16 +2974,16 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3015,16 +2997,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -3069,16 +3051,16 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>5</v>
@@ -3092,16 +3074,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>8</v>
@@ -3146,16 +3128,16 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3169,16 +3151,16 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>9</v>
@@ -3223,16 +3205,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3356,16 +3338,16 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F4">
         <v>92</v>
@@ -3415,16 +3397,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -3474,16 +3456,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3533,16 +3515,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3592,16 +3574,16 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -3651,16 +3633,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -3710,16 +3692,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3769,16 +3751,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>72</v>
@@ -3828,16 +3810,16 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -3887,16 +3869,16 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3946,16 +3928,16 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F14">
         <v>96</v>
@@ -4005,16 +3987,16 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -4064,16 +4046,16 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>72</v>
@@ -4123,16 +4105,16 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -4182,16 +4164,16 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F18">
         <v>92</v>
@@ -4241,16 +4223,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F19">
         <v>92</v>
@@ -4300,16 +4282,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F20">
         <v>92</v>
@@ -4359,16 +4341,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4418,16 +4400,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>72</v>
@@ -4477,16 +4459,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="F23">
         <v>72</v>
@@ -4536,16 +4518,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4598,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4654,16 +4636,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4713,16 +4695,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4772,16 +4754,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4831,16 +4813,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4890,16 +4872,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4949,16 +4931,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F31">
         <v>72</v>
@@ -5008,16 +4990,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -5067,16 +5049,16 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5133,7 +5115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -5173,301 +5155,193 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>46.67</v>
+      </c>
+      <c r="G2">
+        <v>53.33</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>76.67</v>
+      </c>
+      <c r="G3">
+        <v>23.33</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>83.33</v>
+      </c>
+      <c r="G4">
+        <v>16.67</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
+      </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>8.9</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
-      </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9">
-        <v>30</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>30</v>
-      </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>30</v>
-      </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11">
-        <v>30</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>30</v>
-      </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12">
-        <v>30</v>
-      </c>
-      <c r="D12">
-        <v>14</v>
-      </c>
-      <c r="E12">
-        <v>16</v>
-      </c>
-      <c r="F12">
-        <v>46.67</v>
-      </c>
-      <c r="G12">
-        <v>53.33</v>
-      </c>
-      <c r="H12">
-        <v>6.3</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13">
-        <v>30</v>
-      </c>
-      <c r="D13">
-        <v>25</v>
-      </c>
-      <c r="E13">
-        <v>5</v>
-      </c>
-      <c r="F13">
-        <v>83.33</v>
-      </c>
-      <c r="G13">
-        <v>16.67</v>
-      </c>
-      <c r="H13">
-        <v>7.5</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -5478,7 +5352,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5487,2422 +5361,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920002</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920002</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920361</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920361</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920361</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920361</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920003</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920003</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920003</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920003</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920004</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920004</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920004</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920004</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920006</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920006</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920006</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920006</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920007</v>
-      </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920007</v>
-      </c>
-      <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920007</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920007</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920362</v>
-      </c>
-      <c r="B26" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920362</v>
-      </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920362</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920362</v>
-      </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920009</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920009</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920009</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920009</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920011</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920011</v>
-      </c>
-      <c r="B35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" t="s">
-        <v>124</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920011</v>
-      </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920011</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920012</v>
-      </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920012</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920012</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920012</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920013</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920013</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920013</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920013</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920014</v>
-      </c>
-      <c r="B46" t="s">
-        <v>75</v>
-      </c>
-      <c r="C46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920014</v>
-      </c>
-      <c r="B47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920014</v>
-      </c>
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920014</v>
-      </c>
-      <c r="B49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920015</v>
-      </c>
-      <c r="B50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920015</v>
-      </c>
-      <c r="B51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920015</v>
-      </c>
-      <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920015</v>
-      </c>
-      <c r="B53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53" t="s">
-        <v>128</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920016</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" t="s">
-        <v>129</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920016</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920016</v>
-      </c>
-      <c r="B56" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" t="s">
-        <v>102</v>
-      </c>
-      <c r="D56" t="s">
-        <v>129</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920016</v>
-      </c>
-      <c r="B57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920017</v>
-      </c>
-      <c r="B58" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" t="s">
-        <v>130</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920017</v>
-      </c>
-      <c r="B59" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920017</v>
-      </c>
-      <c r="B60" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" t="s">
-        <v>103</v>
-      </c>
-      <c r="D60" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920017</v>
-      </c>
-      <c r="B61" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" t="s">
-        <v>130</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920363</v>
-      </c>
-      <c r="B62" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" t="s">
-        <v>131</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920363</v>
-      </c>
-      <c r="B63" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" t="s">
-        <v>131</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920363</v>
-      </c>
-      <c r="B64" t="s">
-        <v>78</v>
-      </c>
-      <c r="C64" t="s">
-        <v>104</v>
-      </c>
-      <c r="D64" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920363</v>
-      </c>
-      <c r="B65" t="s">
-        <v>78</v>
-      </c>
-      <c r="C65" t="s">
-        <v>104</v>
-      </c>
-      <c r="D65" t="s">
-        <v>131</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920021</v>
-      </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" t="s">
-        <v>132</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920021</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" t="s">
-        <v>132</v>
-      </c>
-      <c r="E67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920021</v>
-      </c>
-      <c r="B68" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" t="s">
-        <v>132</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920021</v>
-      </c>
-      <c r="B69" t="s">
-        <v>79</v>
-      </c>
-      <c r="C69" t="s">
-        <v>105</v>
-      </c>
-      <c r="D69" t="s">
-        <v>132</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920023</v>
-      </c>
-      <c r="B70" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70" t="s">
-        <v>106</v>
-      </c>
-      <c r="D70" t="s">
-        <v>133</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920023</v>
-      </c>
-      <c r="B71" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" t="s">
-        <v>133</v>
-      </c>
-      <c r="E71" t="s">
-        <v>5</v>
-      </c>
-      <c r="F71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920023</v>
-      </c>
-      <c r="B72" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" t="s">
-        <v>106</v>
-      </c>
-      <c r="D72" t="s">
-        <v>133</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920023</v>
-      </c>
-      <c r="B73" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" t="s">
-        <v>106</v>
-      </c>
-      <c r="D73" t="s">
-        <v>133</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920025</v>
-      </c>
-      <c r="B74" t="s">
-        <v>81</v>
-      </c>
-      <c r="C74" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" t="s">
-        <v>134</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920025</v>
-      </c>
-      <c r="B75" t="s">
-        <v>81</v>
-      </c>
-      <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
-        <v>134</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920025</v>
-      </c>
-      <c r="B76" t="s">
-        <v>81</v>
-      </c>
-      <c r="C76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" t="s">
-        <v>134</v>
-      </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920025</v>
-      </c>
-      <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" t="s">
-        <v>107</v>
-      </c>
-      <c r="D77" t="s">
-        <v>134</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920060</v>
-      </c>
-      <c r="B78" t="s">
-        <v>82</v>
-      </c>
-      <c r="C78" t="s">
-        <v>108</v>
-      </c>
-      <c r="D78" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920060</v>
-      </c>
-      <c r="B79" t="s">
-        <v>82</v>
-      </c>
-      <c r="C79" t="s">
-        <v>108</v>
-      </c>
-      <c r="D79" t="s">
-        <v>135</v>
-      </c>
-      <c r="E79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920060</v>
-      </c>
-      <c r="B80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" t="s">
-        <v>108</v>
-      </c>
-      <c r="D80" t="s">
-        <v>135</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920060</v>
-      </c>
-      <c r="B81" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" t="s">
-        <v>108</v>
-      </c>
-      <c r="D81" t="s">
-        <v>135</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920027</v>
-      </c>
-      <c r="B82" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" t="s">
-        <v>109</v>
-      </c>
-      <c r="D82" t="s">
-        <v>136</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920027</v>
-      </c>
-      <c r="B83" t="s">
-        <v>83</v>
-      </c>
-      <c r="C83" t="s">
-        <v>109</v>
-      </c>
-      <c r="D83" t="s">
-        <v>136</v>
-      </c>
-      <c r="E83" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920027</v>
-      </c>
-      <c r="B84" t="s">
-        <v>83</v>
-      </c>
-      <c r="C84" t="s">
-        <v>109</v>
-      </c>
-      <c r="D84" t="s">
-        <v>136</v>
-      </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920027</v>
-      </c>
-      <c r="B85" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" t="s">
-        <v>109</v>
-      </c>
-      <c r="D85" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920028</v>
-      </c>
-      <c r="B86" t="s">
-        <v>84</v>
-      </c>
-      <c r="C86" t="s">
-        <v>76</v>
-      </c>
-      <c r="D86" t="s">
-        <v>137</v>
-      </c>
-      <c r="E86" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920028</v>
-      </c>
-      <c r="B87" t="s">
-        <v>84</v>
-      </c>
-      <c r="C87" t="s">
-        <v>76</v>
-      </c>
-      <c r="D87" t="s">
-        <v>137</v>
-      </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920028</v>
-      </c>
-      <c r="B88" t="s">
-        <v>84</v>
-      </c>
-      <c r="C88" t="s">
-        <v>76</v>
-      </c>
-      <c r="D88" t="s">
-        <v>137</v>
-      </c>
-      <c r="E88" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920028</v>
-      </c>
-      <c r="B89" t="s">
-        <v>84</v>
-      </c>
-      <c r="C89" t="s">
-        <v>76</v>
-      </c>
-      <c r="D89" t="s">
-        <v>137</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920029</v>
-      </c>
-      <c r="B90" t="s">
-        <v>85</v>
-      </c>
-      <c r="C90" t="s">
-        <v>77</v>
-      </c>
-      <c r="D90" t="s">
-        <v>138</v>
-      </c>
-      <c r="E90" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920029</v>
-      </c>
-      <c r="B91" t="s">
-        <v>85</v>
-      </c>
-      <c r="C91" t="s">
-        <v>77</v>
-      </c>
-      <c r="D91" t="s">
-        <v>138</v>
-      </c>
-      <c r="E91" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920029</v>
-      </c>
-      <c r="B92" t="s">
-        <v>85</v>
-      </c>
-      <c r="C92" t="s">
-        <v>77</v>
-      </c>
-      <c r="D92" t="s">
-        <v>138</v>
-      </c>
-      <c r="E92" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920029</v>
-      </c>
-      <c r="B93" t="s">
-        <v>85</v>
-      </c>
-      <c r="C93" t="s">
-        <v>77</v>
-      </c>
-      <c r="D93" t="s">
-        <v>138</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920031</v>
-      </c>
-      <c r="B94" t="s">
-        <v>86</v>
-      </c>
-      <c r="C94" t="s">
-        <v>110</v>
-      </c>
-      <c r="D94" t="s">
-        <v>139</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920031</v>
-      </c>
-      <c r="B95" t="s">
-        <v>86</v>
-      </c>
-      <c r="C95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D95" t="s">
-        <v>139</v>
-      </c>
-      <c r="E95" t="s">
-        <v>5</v>
-      </c>
-      <c r="F95" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>20330051920031</v>
-      </c>
-      <c r="B96" t="s">
-        <v>86</v>
-      </c>
-      <c r="C96" t="s">
-        <v>110</v>
-      </c>
-      <c r="D96" t="s">
-        <v>139</v>
-      </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>20330051920031</v>
-      </c>
-      <c r="B97" t="s">
-        <v>86</v>
-      </c>
-      <c r="C97" t="s">
-        <v>110</v>
-      </c>
-      <c r="D97" t="s">
-        <v>139</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>20330051920032</v>
-      </c>
-      <c r="B98" t="s">
-        <v>87</v>
-      </c>
-      <c r="C98" t="s">
-        <v>111</v>
-      </c>
-      <c r="D98" t="s">
-        <v>120</v>
-      </c>
-      <c r="E98" t="s">
-        <v>6</v>
-      </c>
-      <c r="F98" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>20330051920032</v>
-      </c>
-      <c r="B99" t="s">
-        <v>87</v>
-      </c>
-      <c r="C99" t="s">
-        <v>111</v>
-      </c>
-      <c r="D99" t="s">
-        <v>120</v>
-      </c>
-      <c r="E99" t="s">
-        <v>5</v>
-      </c>
-      <c r="F99" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>20330051920032</v>
-      </c>
-      <c r="B100" t="s">
-        <v>87</v>
-      </c>
-      <c r="C100" t="s">
-        <v>111</v>
-      </c>
-      <c r="D100" t="s">
-        <v>120</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>20330051920032</v>
-      </c>
-      <c r="B101" t="s">
-        <v>87</v>
-      </c>
-      <c r="C101" t="s">
-        <v>111</v>
-      </c>
-      <c r="D101" t="s">
-        <v>120</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>20330051920033</v>
-      </c>
-      <c r="B102" t="s">
-        <v>88</v>
-      </c>
-      <c r="C102" t="s">
-        <v>88</v>
-      </c>
-      <c r="D102" t="s">
-        <v>140</v>
-      </c>
-      <c r="E102" t="s">
-        <v>6</v>
-      </c>
-      <c r="F102" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>20330051920033</v>
-      </c>
-      <c r="B103" t="s">
-        <v>88</v>
-      </c>
-      <c r="C103" t="s">
-        <v>88</v>
-      </c>
-      <c r="D103" t="s">
-        <v>140</v>
-      </c>
-      <c r="E103" t="s">
-        <v>5</v>
-      </c>
-      <c r="F103" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>20330051920033</v>
-      </c>
-      <c r="B104" t="s">
-        <v>88</v>
-      </c>
-      <c r="C104" t="s">
-        <v>88</v>
-      </c>
-      <c r="D104" t="s">
-        <v>140</v>
-      </c>
-      <c r="E104" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>20330051920033</v>
-      </c>
-      <c r="B105" t="s">
-        <v>88</v>
-      </c>
-      <c r="C105" t="s">
-        <v>88</v>
-      </c>
-      <c r="D105" t="s">
-        <v>140</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>20330051920034</v>
-      </c>
-      <c r="B106" t="s">
-        <v>89</v>
-      </c>
-      <c r="C106" t="s">
-        <v>112</v>
-      </c>
-      <c r="D106" t="s">
-        <v>141</v>
-      </c>
-      <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>20330051920034</v>
-      </c>
-      <c r="B107" t="s">
-        <v>89</v>
-      </c>
-      <c r="C107" t="s">
-        <v>112</v>
-      </c>
-      <c r="D107" t="s">
-        <v>141</v>
-      </c>
-      <c r="E107" t="s">
-        <v>5</v>
-      </c>
-      <c r="F107" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>20330051920034</v>
-      </c>
-      <c r="B108" t="s">
-        <v>89</v>
-      </c>
-      <c r="C108" t="s">
-        <v>112</v>
-      </c>
-      <c r="D108" t="s">
-        <v>141</v>
-      </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>20330051920034</v>
-      </c>
-      <c r="B109" t="s">
-        <v>89</v>
-      </c>
-      <c r="C109" t="s">
-        <v>112</v>
-      </c>
-      <c r="D109" t="s">
-        <v>141</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>20330051920035</v>
-      </c>
-      <c r="B110" t="s">
-        <v>90</v>
-      </c>
-      <c r="C110" t="s">
-        <v>113</v>
-      </c>
-      <c r="D110" t="s">
-        <v>142</v>
-      </c>
-      <c r="E110" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>20330051920035</v>
-      </c>
-      <c r="B111" t="s">
-        <v>90</v>
-      </c>
-      <c r="C111" t="s">
-        <v>113</v>
-      </c>
-      <c r="D111" t="s">
-        <v>142</v>
-      </c>
-      <c r="E111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>20330051920035</v>
-      </c>
-      <c r="B112" t="s">
-        <v>90</v>
-      </c>
-      <c r="C112" t="s">
-        <v>113</v>
-      </c>
-      <c r="D112" t="s">
-        <v>142</v>
-      </c>
-      <c r="E112" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>20330051920035</v>
-      </c>
-      <c r="B113" t="s">
-        <v>90</v>
-      </c>
-      <c r="C113" t="s">
-        <v>113</v>
-      </c>
-      <c r="D113" t="s">
-        <v>142</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>20330051920036</v>
-      </c>
-      <c r="B114" t="s">
-        <v>91</v>
-      </c>
-      <c r="C114" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" t="s">
-        <v>118</v>
-      </c>
-      <c r="E114" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>20330051920036</v>
-      </c>
-      <c r="B115" t="s">
-        <v>91</v>
-      </c>
-      <c r="C115" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" t="s">
-        <v>118</v>
-      </c>
-      <c r="E115" t="s">
-        <v>5</v>
-      </c>
-      <c r="F115" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>20330051920036</v>
-      </c>
-      <c r="B116" t="s">
-        <v>91</v>
-      </c>
-      <c r="C116" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" t="s">
-        <v>118</v>
-      </c>
-      <c r="E116" t="s">
-        <v>7</v>
-      </c>
-      <c r="F116" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>20330051920036</v>
-      </c>
-      <c r="B117" t="s">
-        <v>91</v>
-      </c>
-      <c r="C117" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" t="s">
-        <v>118</v>
-      </c>
-      <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>20330051920037</v>
-      </c>
-      <c r="B118" t="s">
-        <v>92</v>
-      </c>
-      <c r="C118" t="s">
-        <v>115</v>
-      </c>
-      <c r="D118" t="s">
-        <v>143</v>
-      </c>
-      <c r="E118" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>20330051920037</v>
-      </c>
-      <c r="B119" t="s">
-        <v>92</v>
-      </c>
-      <c r="C119" t="s">
-        <v>115</v>
-      </c>
-      <c r="D119" t="s">
-        <v>143</v>
-      </c>
-      <c r="E119" t="s">
-        <v>5</v>
-      </c>
-      <c r="F119" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>20330051920037</v>
-      </c>
-      <c r="B120" t="s">
-        <v>92</v>
-      </c>
-      <c r="C120" t="s">
-        <v>115</v>
-      </c>
-      <c r="D120" t="s">
-        <v>143</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>20330051920037</v>
-      </c>
-      <c r="B121" t="s">
-        <v>92</v>
-      </c>
-      <c r="C121" t="s">
-        <v>115</v>
-      </c>
-      <c r="D121" t="s">
-        <v>143</v>
-      </c>
-      <c r="E121" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7921,16 +5395,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>52</v>
@@ -7941,16 +5415,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7958,16 +5432,16 @@
         <v>20330051920361</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7975,16 +5449,16 @@
         <v>20330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7992,16 +5466,16 @@
         <v>20330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8009,16 +5483,16 @@
         <v>20330051920006</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8026,16 +5500,16 @@
         <v>20330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8043,16 +5517,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8060,16 +5534,16 @@
         <v>20330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8077,16 +5551,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8094,16 +5568,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8111,16 +5585,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8128,16 +5602,16 @@
         <v>20330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8145,16 +5619,16 @@
         <v>20330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8162,16 +5636,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8179,16 +5653,16 @@
         <v>20330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8196,16 +5670,16 @@
         <v>20330051920363</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8213,16 +5687,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8230,16 +5704,16 @@
         <v>20330051920023</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8247,16 +5721,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8264,16 +5738,16 @@
         <v>20330051920060</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8281,16 +5755,16 @@
         <v>20330051920027</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8298,16 +5772,16 @@
         <v>20330051920028</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8315,16 +5789,16 @@
         <v>20330051920029</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8332,16 +5806,16 @@
         <v>20330051920031</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8349,16 +5823,16 @@
         <v>20330051920032</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8366,16 +5840,16 @@
         <v>20330051920033</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8383,16 +5857,16 @@
         <v>20330051920034</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8400,16 +5874,16 @@
         <v>20330051920035</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8417,16 +5891,16 @@
         <v>20330051920036</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8434,16 +5908,16 @@
         <v>20330051920037</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8453,7 +5927,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8462,16 +5936,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8481,6 +5955,305 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920013</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920013</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920021</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920021</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920361</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920003</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920014</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920028</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920029</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920033</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920034</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920037</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -4577,7 +4577,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>96</v>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -183,10 +183,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
   </si>
   <si>
     <t>NC</t>
@@ -5190,7 +5199,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -5222,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -5254,7 +5263,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -5286,7 +5295,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -5318,7 +5327,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -5361,16 +5370,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5395,16 +5404,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>52</v>
@@ -5415,13 +5424,13 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5432,13 +5441,13 @@
         <v>20330051920361</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5449,13 +5458,13 @@
         <v>20330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5466,13 +5475,13 @@
         <v>20330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5483,13 +5492,13 @@
         <v>20330051920006</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5500,13 +5509,13 @@
         <v>20330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5517,13 +5526,13 @@
         <v>20330051920362</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5534,13 +5543,13 @@
         <v>20330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5551,13 +5560,13 @@
         <v>20330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5568,13 +5577,13 @@
         <v>20330051920012</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5585,13 +5594,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5602,13 +5611,13 @@
         <v>20330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5619,13 +5628,13 @@
         <v>20330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5636,13 +5645,13 @@
         <v>20330051920016</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5653,13 +5662,13 @@
         <v>20330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5670,13 +5679,13 @@
         <v>20330051920363</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5687,13 +5696,13 @@
         <v>20330051920021</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5704,13 +5713,13 @@
         <v>20330051920023</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5721,13 +5730,13 @@
         <v>20330051920025</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5738,13 +5747,13 @@
         <v>20330051920060</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5755,13 +5764,13 @@
         <v>20330051920027</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5772,13 +5781,13 @@
         <v>20330051920028</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5789,13 +5798,13 @@
         <v>20330051920029</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5806,13 +5815,13 @@
         <v>20330051920031</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5823,13 +5832,13 @@
         <v>20330051920032</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5840,13 +5849,13 @@
         <v>20330051920033</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5857,13 +5866,13 @@
         <v>20330051920034</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5874,13 +5883,13 @@
         <v>20330051920035</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5891,13 +5900,13 @@
         <v>20330051920036</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5908,13 +5917,13 @@
         <v>20330051920037</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5936,16 +5945,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5962,19 +5971,19 @@
         <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5985,13 +5994,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6008,19 +6017,19 @@
         <v>20330051920021</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6031,13 +6040,13 @@
         <v>20330051920021</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6054,13 +6063,13 @@
         <v>20330051920361</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -6077,13 +6086,13 @@
         <v>20330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6100,13 +6109,13 @@
         <v>20330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6123,13 +6132,13 @@
         <v>20330051920014</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6146,13 +6155,13 @@
         <v>20330051920028</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6169,13 +6178,13 @@
         <v>20330051920029</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6192,13 +6201,13 @@
         <v>20330051920033</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6215,13 +6224,13 @@
         <v>20330051920034</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6238,13 +6247,13 @@
         <v>20330051920037</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -210,7 +209,16 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ADELL</t>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>BARRAGAN</t>
@@ -219,25 +227,37 @@
     <t>BERNABE</t>
   </si>
   <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -246,121 +266,16 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
   </si>
   <si>
     <t>JAIR</t>
@@ -369,85 +284,28 @@
     <t>JOSE ANTONIO</t>
   </si>
   <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>DIEGO ADELFO</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JESUS HAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
   </si>
   <si>
     <t>JOSE MATEO</t>
   </si>
   <si>
-    <t>OMAR</t>
-  </si>
-  <si>
     <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>MARCOS SURIEL</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -500,11 +358,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -957,10 +816,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1034,10 +893,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1070,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1111,10 +970,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1147,7 +1006,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1188,10 +1047,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1224,10 +1083,10 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1265,10 +1124,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1342,10 +1201,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1378,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1419,10 +1278,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1455,10 +1314,10 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1496,10 +1355,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1532,7 +1391,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1573,10 +1432,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1650,10 +1509,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1686,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1727,10 +1586,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1766,7 +1625,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1804,10 +1663,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1840,10 +1699,10 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1881,10 +1740,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1917,7 +1776,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1958,10 +1817,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1997,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2035,10 +1894,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2112,10 +1971,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2189,10 +2048,10 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2225,7 +2084,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2266,10 +2125,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2302,10 +2161,10 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2343,10 +2202,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2420,10 +2279,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2456,7 +2315,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2497,10 +2356,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2574,10 +2433,10 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2651,10 +2510,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2728,10 +2587,10 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2767,7 +2626,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2805,10 +2664,10 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2882,10 +2741,10 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2918,10 +2777,10 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2959,10 +2818,10 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2998,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3036,10 +2895,10 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3113,10 +2972,10 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3149,7 +3008,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3190,10 +3049,10 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3229,7 +3088,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3377,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3436,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3495,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3554,10 +3413,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3613,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3672,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3731,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3790,10 +3649,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3849,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3908,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3967,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4026,10 +3885,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4085,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4144,10 +4003,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4203,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4262,10 +4121,10 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4321,10 +4180,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4380,10 +4239,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4439,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4498,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4557,10 +4416,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4616,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4675,10 +4534,10 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4734,10 +4593,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4793,10 +4652,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4852,10 +4711,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4911,10 +4770,10 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -4970,10 +4829,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5029,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5088,10 +4947,10 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5128,6 +4987,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5173,24 +5034,24 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
         <v>14</v>
       </c>
-      <c r="E2">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>46.67</v>
-      </c>
-      <c r="G2">
-        <v>53.33</v>
+      <c r="F2" s="2">
+        <v>53.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46.7</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5210,11 +5071,11 @@
       <c r="E3">
         <v>7</v>
       </c>
-      <c r="F3">
-        <v>76.67</v>
-      </c>
-      <c r="G3">
-        <v>23.33</v>
+      <c r="F3" s="2">
+        <v>76.7</v>
+      </c>
+      <c r="G3" s="2">
+        <v>23.3</v>
       </c>
       <c r="H3">
         <v>7.7</v>
@@ -5222,7 +5083,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5237,24 +5098,24 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>83.33</v>
-      </c>
-      <c r="G4">
-        <v>16.67</v>
+        <v>3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>90</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5274,10 +5135,10 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
@@ -5286,7 +5147,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5306,10 +5167,10 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
@@ -5318,7 +5179,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5338,10 +5199,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
@@ -5350,7 +5211,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5395,548 +5256,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920361</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920006</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920007</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920362</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920009</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920011</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920012</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920013</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920014</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920015</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920016</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920017</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920363</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920021</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920023</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920025</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920060</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920027</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920028</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920029</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920031</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920032</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920033</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>20330051920034</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>20330051920035</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>20330051920036</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>20330051920037</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>140</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5968,16 +5288,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5991,16 +5311,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6014,16 +5334,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920021</v>
+        <v>20330051920013</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6037,16 +5357,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920021</v>
+        <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6060,22 +5380,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920361</v>
+        <v>20330051920021</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6083,16 +5403,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920003</v>
+        <v>20330051920021</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6106,22 +5426,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920007</v>
+        <v>20330051920060</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6129,16 +5449,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920014</v>
+        <v>20330051920060</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6152,16 +5472,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920028</v>
+        <v>20330051920361</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6175,16 +5495,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920029</v>
+        <v>20330051920003</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6198,16 +5518,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920033</v>
+        <v>20330051920011</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6221,16 +5541,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920034</v>
+        <v>20330051920012</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6244,16 +5564,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920037</v>
+        <v>20330051920028</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6262,6 +5582,52 @@
         <v>54</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920029</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920033</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -810,10 +810,10 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -846,10 +846,10 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -887,10 +887,10 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -964,10 +964,10 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -1000,10 +1000,10 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1041,10 +1041,10 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1077,10 +1077,10 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1118,10 +1118,10 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1195,10 +1195,10 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1272,10 +1272,10 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1308,10 +1308,10 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1349,10 +1349,10 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1426,10 +1426,10 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1462,7 +1462,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1503,10 +1503,10 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1580,10 +1580,10 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1616,10 +1616,10 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1657,10 +1657,10 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1693,10 +1693,10 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1734,10 +1734,10 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1770,10 +1770,10 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1811,10 +1811,10 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1888,10 +1888,10 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -1965,10 +1965,10 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2042,10 +2042,10 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2078,10 +2078,10 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2119,10 +2119,10 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -2155,10 +2155,10 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2196,10 +2196,10 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2273,10 +2273,10 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -2350,10 +2350,10 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2427,10 +2427,10 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>7</v>
@@ -2504,10 +2504,10 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2581,10 +2581,10 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2658,10 +2658,10 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2735,10 +2735,10 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -2812,10 +2812,10 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>8</v>
@@ -2889,10 +2889,10 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -2966,10 +2966,10 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3043,10 +3043,10 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L4">
         <v>76</v>
@@ -3289,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L5">
         <v>92</v>
@@ -3348,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3466,10 +3466,10 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L9">
         <v>92</v>
@@ -3584,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3643,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L11">
         <v>76</v>
@@ -3702,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -3761,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3820,10 +3820,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L14">
         <v>96</v>
@@ -3879,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L17">
         <v>92</v>
@@ -4056,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L19">
         <v>96</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L20">
         <v>92</v>
@@ -4233,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L21">
         <v>92</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L22">
         <v>88</v>
@@ -4351,10 +4351,10 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L23">
         <v>88</v>
@@ -4410,10 +4410,10 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L24">
         <v>92</v>
@@ -4469,10 +4469,10 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -4528,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4587,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4646,10 +4646,10 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L28">
         <v>76</v>
@@ -4705,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4764,10 +4764,10 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4823,10 +4823,10 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L31">
         <v>80</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L32">
         <v>96</v>
@@ -4941,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L33">
         <v>96</v>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5206,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -215,21 +215,21 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
@@ -245,21 +245,21 @@
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -272,22 +272,22 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
     <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -807,7 +807,7 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -843,7 +843,7 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -884,7 +884,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -920,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -961,7 +961,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -997,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1038,7 +1038,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -1074,7 +1074,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1115,7 +1115,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1151,7 +1151,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1192,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -1346,7 +1346,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1423,7 +1423,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1500,7 +1500,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1536,7 +1536,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1654,7 +1654,7 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -1731,7 +1731,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1808,7 +1808,7 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -1844,7 +1844,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -1885,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -1962,7 +1962,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -2039,7 +2039,7 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>8</v>
@@ -2075,7 +2075,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2116,7 +2116,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -2152,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2193,7 +2193,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -2270,7 +2270,7 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2347,7 +2347,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -2424,7 +2424,7 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2501,7 +2501,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2537,7 +2537,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2578,7 +2578,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2655,7 +2655,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -2691,7 +2691,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2732,7 +2732,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2768,7 +2768,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2809,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>9</v>
@@ -2845,7 +2845,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -2886,7 +2886,7 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -2963,7 +2963,7 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -3040,7 +3040,7 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -3076,7 +3076,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>120</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>120</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>120</v>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>120</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>120</v>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>120</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>120</v>
@@ -3640,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>120</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>120</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>120</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>120</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>120</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>120</v>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>120</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>120</v>
@@ -4112,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>120</v>
@@ -4171,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>120</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>120</v>
@@ -4289,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>120</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>120</v>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>120</v>
@@ -4466,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>120</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>120</v>
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>120</v>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>120</v>
@@ -4702,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>120</v>
@@ -4761,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>120</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>120</v>
@@ -4879,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>120</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>120</v>
@@ -5066,19 +5066,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5256,7 +5256,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920021</v>
+        <v>20330051920060</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920021</v>
+        <v>20330051920060</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920060</v>
+        <v>20330051920361</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -5438,10 +5438,10 @@
         <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5449,16 +5449,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920060</v>
+        <v>20330051920003</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5472,16 +5472,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920361</v>
+        <v>20330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -5495,7 +5495,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920003</v>
+        <v>20330051920012</v>
       </c>
       <c r="B11" t="s">
         <v>68</v>
@@ -5504,7 +5504,7 @@
         <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920011</v>
+        <v>20330051920021</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
@@ -5527,7 +5527,7 @@
         <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -5541,16 +5541,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920012</v>
+        <v>20330051920028</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5564,16 +5564,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920028</v>
+        <v>20330051920029</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5587,16 +5587,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920029</v>
+        <v>20330051920033</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5605,29 +5605,6 @@
         <v>54</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920033</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -804,7 +804,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -881,7 +881,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -958,7 +958,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1035,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -1112,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -1148,7 +1148,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1189,7 +1189,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>8</v>
@@ -1266,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1343,7 +1343,7 @@
         <v>4</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1420,7 +1420,7 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1497,7 +1497,7 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1533,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1574,7 +1574,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -1651,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -1728,7 +1728,7 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1805,7 +1805,7 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -1882,7 +1882,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -1918,7 +1918,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -1959,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2036,7 +2036,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2113,7 +2113,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>8</v>
@@ -2190,7 +2190,7 @@
         <v>4</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2267,7 +2267,7 @@
         <v>4</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2344,7 +2344,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -2380,7 +2380,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -2421,7 +2421,7 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -2498,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -2575,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>7</v>
@@ -2652,7 +2652,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2729,7 +2729,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -2806,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -2883,7 +2883,7 @@
         <v>4</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -2960,7 +2960,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>8</v>
@@ -2996,7 +2996,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>9</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>7</v>
@@ -3224,7 +3224,7 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3283,7 +3283,7 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -3342,7 +3342,7 @@
         <v>92</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -3401,7 +3401,7 @@
         <v>92</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -3460,7 +3460,7 @@
         <v>92</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3519,7 +3519,7 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -3578,7 +3578,7 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -3637,7 +3637,7 @@
         <v>76</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -3696,7 +3696,7 @@
         <v>76</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -3755,7 +3755,7 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -3814,7 +3814,7 @@
         <v>92</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -3873,7 +3873,7 @@
         <v>92</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -3932,7 +3932,7 @@
         <v>76</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3991,7 +3991,7 @@
         <v>92</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -4050,7 +4050,7 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -4109,7 +4109,7 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4168,7 +4168,7 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -4227,7 +4227,7 @@
         <v>92</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -4286,7 +4286,7 @@
         <v>76</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -4345,7 +4345,7 @@
         <v>76</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -4404,7 +4404,7 @@
         <v>92</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -4463,7 +4463,7 @@
         <v>92</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -4522,7 +4522,7 @@
         <v>92</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -4581,7 +4581,7 @@
         <v>92</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4640,7 +4640,7 @@
         <v>92</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -4699,7 +4699,7 @@
         <v>92</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -4758,7 +4758,7 @@
         <v>92</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I30">
         <v>100</v>
@@ -4817,7 +4817,7 @@
         <v>76</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I31">
         <v>100</v>
@@ -4876,7 +4876,7 @@
         <v>92</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -4935,7 +4935,7 @@
         <v>92</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5142,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -3209,55 +3209,55 @@
         <v>100</v>
       </c>
       <c r="C4">
+        <v>95.8</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
         <v>92</v>
-      </c>
-      <c r="D4">
-        <v>130</v>
-      </c>
-      <c r="E4">
-        <v>115</v>
       </c>
       <c r="F4">
         <v>92</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>95.7</v>
       </c>
       <c r="L4">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3268,55 +3268,55 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>96</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M5">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3327,55 +3327,55 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3386,55 +3386,55 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3445,55 +3445,55 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
       </c>
       <c r="G8">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3504,55 +3504,55 @@
         <v>100</v>
       </c>
       <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>96</v>
       </c>
-      <c r="D9">
-        <v>130</v>
-      </c>
-      <c r="E9">
-        <v>125</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>120</v>
-      </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9">
-        <v>120</v>
-      </c>
-      <c r="K9">
-        <v>110</v>
-      </c>
-      <c r="L9">
-        <v>92</v>
-      </c>
       <c r="M9">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3563,55 +3563,55 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3622,55 +3622,55 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="D11">
-        <v>90</v>
+        <v>69.2</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>72</v>
       </c>
       <c r="G11">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="K11">
-        <v>110</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L11">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M11">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="P11">
         <v>84</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
       <c r="Q11">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3681,55 +3681,55 @@
         <v>100</v>
       </c>
       <c r="C12">
+        <v>83.3</v>
+      </c>
+      <c r="D12">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E12">
         <v>80</v>
       </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
       <c r="F12">
         <v>100</v>
       </c>
       <c r="G12">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="K12">
-        <v>110</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3740,55 +3740,55 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3799,55 +3799,55 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D14">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E14">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>96</v>
       </c>
       <c r="G14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>96</v>
       </c>
       <c r="M14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3858,55 +3858,55 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D15">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>96</v>
       </c>
       <c r="G15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M15">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3917,55 +3917,55 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>76</v>
+        <v>79.2</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F16">
         <v>72</v>
       </c>
       <c r="G16">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="J16">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="K16">
-        <v>110</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="M16">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>89.8</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3976,55 +3976,55 @@
         <v>100</v>
       </c>
       <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>100</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>96</v>
       </c>
-      <c r="D17">
-        <v>130</v>
-      </c>
-      <c r="E17">
-        <v>125</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>92</v>
-      </c>
-      <c r="H17">
-        <v>120</v>
-      </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
-      <c r="J17">
-        <v>120</v>
-      </c>
-      <c r="K17">
-        <v>110</v>
-      </c>
-      <c r="L17">
-        <v>92</v>
-      </c>
       <c r="M17">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4035,55 +4035,55 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>92</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4094,55 +4094,55 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D19">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>92</v>
       </c>
       <c r="G19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M19">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4153,55 +4153,55 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D20">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E20">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>92</v>
       </c>
       <c r="G20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>92</v>
       </c>
       <c r="M20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4212,55 +4212,55 @@
         <v>100</v>
       </c>
       <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>100</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>96</v>
       </c>
-      <c r="D21">
-        <v>130</v>
-      </c>
-      <c r="E21">
-        <v>125</v>
-      </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>92</v>
-      </c>
-      <c r="H21">
-        <v>120</v>
-      </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
-      <c r="J21">
-        <v>120</v>
-      </c>
-      <c r="K21">
-        <v>110</v>
-      </c>
-      <c r="L21">
-        <v>92</v>
-      </c>
       <c r="M21">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4271,55 +4271,55 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="D22">
-        <v>90</v>
+        <v>69.2</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F22">
         <v>72</v>
       </c>
       <c r="G22">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J22">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="K22">
-        <v>110</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L22">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M22">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="P22">
         <v>84</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
       <c r="Q22">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4330,55 +4330,55 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="D23">
-        <v>110</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E23">
-        <v>112.5</v>
+        <v>90</v>
       </c>
       <c r="F23">
         <v>72</v>
       </c>
       <c r="G23">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="J23">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="K23">
-        <v>110</v>
+        <v>94.7</v>
       </c>
       <c r="L23">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M23">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4389,55 +4389,55 @@
         <v>100</v>
       </c>
       <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
         <v>96</v>
       </c>
-      <c r="D24">
-        <v>130</v>
-      </c>
-      <c r="E24">
-        <v>125</v>
-      </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
-      <c r="G24">
-        <v>92</v>
-      </c>
-      <c r="H24">
-        <v>120</v>
-      </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>120</v>
-      </c>
-      <c r="K24">
-        <v>110</v>
-      </c>
-      <c r="L24">
-        <v>92</v>
-      </c>
       <c r="M24">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4448,55 +4448,55 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4507,55 +4507,55 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D26">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E26">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4566,55 +4566,55 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D27">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E27">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
       </c>
       <c r="J27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4625,55 +4625,55 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E28">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="M28">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4684,55 +4684,55 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E29">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4743,55 +4743,55 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D30">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
       </c>
       <c r="G30">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4802,55 +4802,55 @@
         <v>20</v>
       </c>
       <c r="C31">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="D31">
-        <v>90</v>
+        <v>69.2</v>
       </c>
       <c r="E31">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F31">
         <v>72</v>
       </c>
       <c r="G31">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="H31">
+        <v>63.6</v>
+      </c>
+      <c r="I31">
+        <v>91.8</v>
+      </c>
+      <c r="J31">
+        <v>84</v>
+      </c>
+      <c r="K31">
+        <v>83</v>
+      </c>
+      <c r="L31">
         <v>76</v>
       </c>
-      <c r="H31">
-        <v>120</v>
-      </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
-      <c r="J31">
-        <v>120</v>
-      </c>
-      <c r="K31">
-        <v>110</v>
-      </c>
-      <c r="L31">
-        <v>80</v>
-      </c>
       <c r="M31">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N31">
+        <v>63.6</v>
+      </c>
+      <c r="O31">
+        <v>91.8</v>
+      </c>
+      <c r="P31">
         <v>84</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
       <c r="Q31">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4861,55 +4861,55 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D32">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E32">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>100</v>
       </c>
       <c r="J32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M32">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4920,55 +4920,55 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D33">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
       </c>
       <c r="G33">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>100</v>
       </c>
       <c r="J33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M33">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6AEM - Estadisticos 20222.xlsx
+++ b/grupos/6AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
@@ -209,34 +209,25 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -245,25 +236,16 @@
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>VINALAY</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>MARCOS SURIEL</t>
   </si>
   <si>
     <t>JOSUE</t>
@@ -272,31 +254,13 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
     <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
   </si>
 </sst>
 </file>
@@ -822,22 +786,22 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -852,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -899,22 +863,22 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -923,16 +887,16 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -976,22 +940,22 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1006,10 +970,10 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1053,22 +1017,22 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1130,22 +1094,22 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1207,28 +1171,28 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1284,22 +1248,22 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1361,28 +1325,28 @@
         <v>4</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1391,7 +1355,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1438,37 +1402,37 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1515,22 +1479,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1539,10 +1503,10 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1592,22 +1556,22 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1625,7 +1589,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1669,22 +1633,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1702,7 +1666,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1746,28 +1710,28 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1823,22 +1787,22 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1847,10 +1811,10 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1900,22 +1864,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1977,22 +1941,22 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2007,10 +1971,10 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2054,22 +2018,22 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2087,7 +2051,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2131,22 +2095,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2161,7 +2125,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2208,28 +2172,28 @@
         <v>4</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>7</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2238,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2285,28 +2249,28 @@
         <v>4</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -2315,7 +2279,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2362,22 +2326,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2439,22 +2403,22 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2469,10 +2433,10 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2516,22 +2480,22 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2540,16 +2504,16 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2593,22 +2557,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2670,22 +2634,22 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2703,7 +2667,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2747,22 +2711,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -2777,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2824,22 +2788,22 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2857,7 +2821,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2901,37 +2865,37 @@
         <v>4</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -2978,22 +2942,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3008,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3055,22 +3019,22 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3245,16 +3209,16 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>84</v>
+        <v>89.3</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3304,7 +3268,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3313,7 +3277,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3363,7 +3327,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3422,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3481,7 +3445,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3540,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3549,7 +3513,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3658,19 +3622,19 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="P11">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="Q11">
-        <v>89.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="R11">
-        <v>74</v>
+        <v>82.7</v>
       </c>
       <c r="S11">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3717,19 +3681,19 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>91.8</v>
+        <v>91.3</v>
       </c>
       <c r="P12">
-        <v>88</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q12">
-        <v>89.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3776,7 +3740,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3835,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3844,7 +3808,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3894,7 +3858,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3903,7 +3867,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3953,19 +3917,19 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>89.8</v>
+        <v>91.3</v>
       </c>
       <c r="P16">
-        <v>88</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q16">
-        <v>89.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="R16">
-        <v>86</v>
+        <v>90.7</v>
       </c>
       <c r="S16">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4012,7 +3976,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4021,7 +3985,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -4071,7 +4035,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4080,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4130,7 +4094,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4139,7 +4103,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4189,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4198,7 +4162,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4248,7 +4212,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4257,7 +4221,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4307,19 +4271,19 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>93.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="P22">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="Q22">
-        <v>89.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="R22">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="S22">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4366,19 +4330,19 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="P23">
-        <v>92</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
-        <v>94.7</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R23">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="S23">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4425,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4434,7 +4398,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4484,7 +4448,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4543,7 +4507,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4661,7 +4625,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -4670,7 +4634,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4720,7 +4684,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -4779,7 +4743,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -4788,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -4835,22 +4799,22 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N31">
-        <v>63.6</v>
+        <v>75</v>
       </c>
       <c r="O31">
-        <v>91.8</v>
+        <v>93.8</v>
       </c>
       <c r="P31">
+        <v>87.5</v>
+      </c>
+      <c r="Q31">
+        <v>87.5</v>
+      </c>
+      <c r="R31">
         <v>84</v>
       </c>
-      <c r="Q31">
-        <v>83</v>
-      </c>
-      <c r="R31">
-        <v>76</v>
-      </c>
       <c r="S31">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4906,7 +4870,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -4956,7 +4920,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -4965,7 +4929,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5034,19 +4998,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>53.3</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>46.7</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5057,7 +5021,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5066,19 +5030,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>80</v>
+        <v>96.7</v>
       </c>
       <c r="G3" s="2">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5098,19 +5062,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5121,7 +5085,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5142,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5174,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5206,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5256,7 +5220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5288,19 +5252,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920362</v>
+        <v>20330051920035</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -5311,16 +5275,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920362</v>
+        <v>20330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5334,22 +5298,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5360,13 +5324,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5380,22 +5344,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920060</v>
+        <v>20330051920016</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5403,16 +5367,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920060</v>
+        <v>20330051920025</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5426,16 +5390,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920361</v>
+        <v>20330051920060</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5444,167 +5408,6 @@
         <v>54</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920003</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920011</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920012</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920021</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920028</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920029</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920033</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>
